--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_184_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_184_R19.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5751</v>
+        <v>6.572</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2834</v>
+        <v>4.6405</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2917</v>
+        <v>1.9315</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9094</v>
+        <v>5.0378</v>
       </c>
       <c r="H2" t="n">
-        <v>0.287</v>
+        <v>3.1007</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6224</v>
+        <v>1.9371</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4491</v>
+        <v>5.6742</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8234</v>
+        <v>3.6803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6257</v>
+        <v>1.9939</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.6364</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5365</v>
+        <v>-0.5796</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0033</v>
+        <v>-0.0568</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8487</v>
+        <v>0.6065</v>
       </c>
       <c r="T2" t="n">
-        <v>3.409</v>
+        <v>0.1261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4397</v>
+        <v>0.4804</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2278</v>
+        <v>4.3064</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3299</v>
+        <v>3.1346</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8979</v>
+        <v>1.1718</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0378</v>
+        <v>3.4316</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1007</v>
+        <v>-0.9014</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9371</v>
+        <v>4.3331</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6742</v>
+        <v>2.8278</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6803</v>
+        <v>-0.6687</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9939</v>
+        <v>3.4965</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6364</v>
+        <v>0.6039</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5796</v>
+        <v>-0.2327</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0568</v>
+        <v>0.8366</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2623</v>
+        <v>0.3233</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>0.3068</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4468</v>
+        <v>0.0165</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1164</v>
+        <v>4.2332</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8733</v>
+        <v>3.0424</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2431</v>
+        <v>1.1909</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4939</v>
+        <v>0.9094</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0695</v>
+        <v>0.287</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5756</v>
+        <v>0.6224</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5519</v>
+        <v>1.4491</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3346</v>
+        <v>0.8234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2173</v>
+        <v>0.6257</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.058</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2651</v>
+        <v>-0.5365</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7929</v>
+        <v>-0.0033</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9988</v>
+        <v>1.5068</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3214</v>
+        <v>1.1679</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6774</v>
+        <v>0.3389</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0204</v>
+        <v>2.9786</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0167</v>
+        <v>2.0044</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0038</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4316</v>
+        <v>0.4939</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9014</v>
+        <v>1.0695</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3331</v>
+        <v>-0.5756</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8278</v>
+        <v>1.5519</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6687</v>
+        <v>1.3346</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4965</v>
+        <v>0.2173</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6039</v>
+        <v>-1.058</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2327</v>
+        <v>-0.2651</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8366</v>
+        <v>-0.7929</v>
       </c>
       <c r="P5" t="n">
         <v>1.6237</v>
@@ -844,28 +844,28 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0373</v>
+        <v>0.861</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.4525</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1516</v>
+        <v>0.4086</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4113</v>
+        <v>1.2971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6359</v>
+        <v>0.8452</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7754</v>
+        <v>0.4519</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3787</v>
+        <v>-1.2979</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.275</v>
+        <v>0.2714</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1038</v>
+        <v>-1.5693</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8125</v>
+        <v>-0.3042</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1912</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0037</v>
+        <v>-1.1445</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1912</v>
+        <v>-0.9937</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0838</v>
+        <v>-0.5688</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1074</v>
+        <v>-0.4248</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3983</v>
+        <v>0.2546</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1766</v>
+        <v>-0.0312</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5749</v>
+        <v>0.2858</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7574</v>
+        <v>0.9654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1375</v>
+        <v>0.8285</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6199</v>
+        <v>0.1369</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2979</v>
+        <v>-1.3787</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2714</v>
+        <v>-1.275</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5693</v>
+        <v>-0.1038</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3042</v>
+        <v>0.8125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.1912</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1445</v>
+        <v>1.0037</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9937</v>
+        <v>-2.1912</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5688</v>
+        <v>-1.0838</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4248</v>
+        <v>-1.1074</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2851</v>
+        <v>0.9524</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7389</v>
+        <v>0.016</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4538</v>
+        <v>0.9364</v>
       </c>
       <c r="V7" t="n">
-        <v>3.5002</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.5002</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5617</v>
+        <v>0.8477</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7278</v>
+        <v>-0.6099</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2895</v>
+        <v>1.4575</v>
       </c>
       <c r="G8" t="n">
         <v>0.5138</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1867</v>
+        <v>0.0993</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U8" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V8" t="n">
         <v>0.9304</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2399</v>
+        <v>0.2826</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4015</v>
+        <v>-1.8117</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1615</v>
+        <v>2.0943</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2616</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5324</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>0.067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8321</v>
+        <v>-1.1179</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1923</v>
+        <v>-1.1532</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3602</v>
+        <v>0.0353</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8654</v>
+        <v>0.1651</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8955</v>
+        <v>-1.9795</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0301</v>
+        <v>2.1446</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1468</v>
+        <v>1.0766</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0229</v>
+        <v>-1.7036</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1239</v>
+        <v>2.7802</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7186</v>
+        <v>-0.9115</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8726</v>
+        <v>-0.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>0.154</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3374</v>
+        <v>0.2684</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1142</v>
+        <v>0.1772</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2232</v>
+        <v>0.0912</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9834</v>
+        <v>-1.6977</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5818</v>
+        <v>-3.1923</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4016</v>
+        <v>1.4946</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1651</v>
+        <v>-2.8654</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9795</v>
+        <v>-2.8955</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1446</v>
+        <v>0.0301</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0766</v>
+        <v>-2.1468</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7036</v>
+        <v>-2.0229</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7802</v>
+        <v>-0.1239</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9115</v>
+        <v>-0.7186</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2759</v>
+        <v>-0.8726</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.597</v>
+        <v>0.4718</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>0.1142</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3457</v>
+        <v>0.3576</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8698</v>
+        <v>-5.5491</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4396</v>
+        <v>-3.4213</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4302</v>
+        <v>-2.1278</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2525</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7771</v>
+        <v>0.5436</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.187</v>
+        <v>-0.1687</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4099</v>
+        <v>0.7123</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.7449</v>
+        <v>13.1183</v>
       </c>
       <c r="E13" t="n">
-        <v>3.933700000000002</v>
+        <v>4.3072</v>
       </c>
       <c r="F13" t="n">
-        <v>8.811200000000003</v>
+        <v>8.811199999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5045000000000011</v>
@@ -1438,7 +1438,7 @@
         <v>-5.773800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2694</v>
+        <v>5.269400000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.646</v>
@@ -1468,13 +1468,13 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>5.504499999999999</v>
+        <v>5.8778</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6737</v>
+        <v>2.047</v>
       </c>
       <c r="U13" t="n">
-        <v>3.8307</v>
+        <v>3.830900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>3.105900000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2838</v>
+        <v>1.0603</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9345</v>
+        <v>0.2964</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3493</v>
+        <v>0.7639</v>
       </c>
       <c r="G14" t="n">
-        <v>1.859</v>
+        <v>0.5876</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2604</v>
+        <v>-0.1452</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4015</v>
+        <v>0.7328</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9054</v>
+        <v>1.1414</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8317</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0736</v>
+        <v>1.0539</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0464</v>
+        <v>-0.5538</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4287</v>
+        <v>-0.2327</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4751</v>
+        <v>-0.3211</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.6871</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1889</v>
+        <v>-0.845</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1067</v>
+        <v>0.1579</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1776</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1785</v>
+        <v>0.5806</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9991</v>
+        <v>0.2485</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5876</v>
+        <v>1.859</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1452</v>
+        <v>2.2604</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7328</v>
+        <v>-0.4015</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1414</v>
+        <v>1.9054</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.8317</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0539</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5538</v>
+        <v>-0.0464</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2327</v>
+        <v>0.4287</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3211</v>
+        <v>-0.4751</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5698</v>
+        <v>-0.3725</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.165</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3932</v>
+        <v>-0.2076</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0176</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1851</v>
+        <v>0.6803</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1675</v>
+        <v>-0.1617</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6233</v>
+        <v>0.287</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7106</v>
+        <v>0.6015</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0873</v>
+        <v>-0.3145</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3276</v>
+        <v>0.6408</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9865</v>
+        <v>0.3732</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3412</v>
+        <v>0.2676</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7043</v>
+        <v>-0.3538</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2759</v>
+        <v>0.2283</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4285</v>
+        <v>-0.5821</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.358</v>
+        <v>-0.7863</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3031</v>
+        <v>0.0395</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0549</v>
+        <v>-0.8259</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8919</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0336</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7874</v>
+        <v>0.4678</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6803</v>
+        <v>0.7133</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1071</v>
+        <v>-0.2455</v>
       </c>
       <c r="G17" t="n">
-        <v>0.287</v>
+        <v>0.6233</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6015</v>
+        <v>1.7106</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3145</v>
+        <v>-1.0873</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6408</v>
+        <v>2.3276</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3732</v>
+        <v>1.9865</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2676</v>
+        <v>0.3412</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3538</v>
+        <v>-1.7043</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2283</v>
+        <v>-0.2759</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5821</v>
+        <v>-1.4285</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5175</v>
+        <v>-0.1918</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0395</v>
+        <v>-0.1687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.0231</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>1.8919</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.0336</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0143</v>
+        <v>0.2744</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0579</v>
+        <v>1.0893</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0436</v>
+        <v>-0.8149</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.194</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0168</v>
+        <v>0.0504</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2108</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0168</v>
+        <v>1.7103</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0168</v>
+        <v>0.1043</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.606</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2108</v>
+        <v>-0.9003</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.0539</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2108</v>
+        <v>-0.8464</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0523</v>
+        <v>-0.3912</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0747</v>
+        <v>-0.621</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.2298</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.068</v>
+        <v>0.0193</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9714</v>
+        <v>-0.0579</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0394</v>
+        <v>0.0772</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.194</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0504</v>
+        <v>0.0168</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7596000000000001</v>
+        <v>-0.2108</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7103</v>
+        <v>0.0168</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1043</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
-        <v>1.606</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9003</v>
+        <v>-0.2108</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0539</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8464</v>
+        <v>-0.2108</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7336</v>
+        <v>-0.0187</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0053</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.213</v>
+        <v>-0.4495</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3305</v>
+        <v>0.1413</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8825</v>
+        <v>-0.5909</v>
       </c>
       <c r="G20" t="n">
         <v>0.7157</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1606</v>
+        <v>-0.3971</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5632</v>
+        <v>-0.2715</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9567</v>
+        <v>-1.7645</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8658</v>
+        <v>-0.394</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0909</v>
+        <v>-1.3705</v>
       </c>
       <c r="G21" t="n">
         <v>0.8512999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2719</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0376</v>
+        <v>-0.5658</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7657</v>
+        <v>0.4861</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6083</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9772</v>
+        <v>-3.9176</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0048</v>
+        <v>-3.9587</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0276</v>
+        <v>0.0411</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1736</v>
+        <v>-4.2675</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0973</v>
+        <v>-0.5869</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2709</v>
+        <v>-3.6806</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4058</v>
+        <v>-3.1884</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1785</v>
+        <v>-0.6687</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2272</v>
+        <v>-2.5197</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2321</v>
+        <v>-1.0791</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2759</v>
+        <v>0.0818</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0437</v>
+        <v>-1.1609</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2257</v>
+        <v>-0.5779</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2284</v>
+        <v>-0.7703</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4541</v>
+        <v>0.1924</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3044</v>
+        <v>-3.99</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0767</v>
+        <v>-4.7125</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2278</v>
+        <v>0.7226</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.2675</v>
+        <v>0.1736</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5869</v>
+        <v>-0.0973</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6806</v>
+        <v>0.2709</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1884</v>
+        <v>0.4058</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6687</v>
+        <v>0.1785</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5197</v>
+        <v>0.2272</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0791</v>
+        <v>-0.2321</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0818</v>
+        <v>-0.2759</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1609</v>
+        <v>0.0437</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9278</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9647</v>
+        <v>-1.2384</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8883</v>
+        <v>-0.4793</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0764</v>
+        <v>-0.7591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4775</v>
+        <v>-5.0064</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4253</v>
+        <v>-3.1894</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0523</v>
+        <v>-1.817</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9415</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4485</v>
+        <v>0.0226</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1577</v>
+        <v>0.0775</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.7447</v>
+        <v>-11.9585</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.811199999999999</v>
+        <v>-8.811299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.9337</v>
+        <v>-3.1472</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5044999999999997</v>
+        <v>0.5044999999999993</v>
       </c>
       <c r="H25" t="n">
         <v>5.773900000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.269600000000001</v>
+        <v>-5.2696</v>
       </c>
       <c r="J25" t="n">
-        <v>8.1503</v>
+        <v>8.150300000000001</v>
       </c>
       <c r="K25" t="n">
         <v>5.7422</v>
@@ -2386,10 +2386,10 @@
         <v>2.4081</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.645700000000001</v>
+        <v>-7.6457</v>
       </c>
       <c r="N25" t="n">
-        <v>0.03170000000000001</v>
+        <v>0.03170000000000006</v>
       </c>
       <c r="O25" t="n">
         <v>-7.6777</v>
@@ -2404,13 +2404,13 @@
         <v>11.5977</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.504499999999999</v>
+        <v>-4.718100000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.8309</v>
+        <v>-3.8308</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6736</v>
+        <v>-0.8875</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1059</v>
